--- a/summer_2025_schedule/rt_projected_schedule.xlsx
+++ b/summer_2025_schedule/rt_projected_schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\OneDrive - University of Southern California\Github\BTG\summer_2025_schedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/USC Shared Folders/BTG/BTG/summer_2025_schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D05A288-97EC-4342-8D36-28A4C29B1B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{709B4272-95D4-4CE2-9E15-1F20C641EF30}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{709B4272-95D4-4CE2-9E15-1F20C641EF30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
